--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="427">
   <si>
     <t>Materials</t>
   </si>
@@ -453,13 +453,19 @@
     <t>tin 4 / cassiterite 6</t>
   </si>
   <si>
+    <t>normal_amethyst</t>
+  </si>
+  <si>
+    <t>red_garnet 10 / almandine 15 / amethyst 40 / opal 40</t>
+  </si>
+  <si>
+    <t>28%</t>
+  </si>
+  <si>
     <t>normal_asbestos_dry</t>
   </si>
   <si>
     <t>cassiterite 6 / asbestos 1</t>
-  </si>
-  <si>
-    <t>28%</t>
   </si>
   <si>
     <t>#tfg:earth/is_dry</t>
@@ -1377,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ76"/>
+  <dimension ref="A1:AQ77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.531091690063477" customWidth="1" style="4"/>
@@ -6044,25 +6050,25 @@
         <v>70</v>
       </c>
       <c r="G41" s="3">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>147</v>
       </c>
       <c r="I41" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J41" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="P41" s="2" t="s">
-        <v>48</v>
+      <c r="P41" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q41" s="2" t="s">
         <v>48</v>
@@ -6070,68 +6076,68 @@
       <c r="R41" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V41" s="1" t="s">
-        <v>49</v>
+      <c r="S41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="W41" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="X41" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y41" s="1" t="s">
-        <v>49</v>
+      <c r="X41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y41" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Z41" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB41" s="2" t="s">
-        <v>48</v>
+      <c r="AA41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB41" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AC41" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF41" s="1" t="s">
-        <v>49</v>
+      <c r="AD41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF41" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AG41" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH41" s="1" t="s">
-        <v>49</v>
+      <c r="AH41" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AI41" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ41" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AL41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM41" s="1" t="s">
-        <v>49</v>
+      <c r="AJ41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM41" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AN41" s="1" t="s">
         <v>49</v>
@@ -6145,13 +6151,13 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D42" s="3">
         <v>10</v>
@@ -6160,19 +6166,19 @@
         <v>70</v>
       </c>
       <c r="G42" s="3">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>147</v>
       </c>
       <c r="I42" s="3">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J42" s="3">
         <v>10</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>47</v>
+        <v>150</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>48</v>
@@ -6186,17 +6192,17 @@
       <c r="R42" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S42" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T42" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U42" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V42" s="2" t="s">
-        <v>48</v>
+      <c r="S42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V42" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="W42" s="2" t="s">
         <v>48</v>
@@ -6204,8 +6210,8 @@
       <c r="X42" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y42" s="2" t="s">
-        <v>48</v>
+      <c r="Y42" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Z42" s="2" t="s">
         <v>48</v>
@@ -6219,8 +6225,8 @@
       <c r="AC42" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD42" s="2" t="s">
-        <v>48</v>
+      <c r="AD42" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AE42" s="1" t="s">
         <v>49</v>
@@ -6243,8 +6249,8 @@
       <c r="AK42" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AL42" s="2" t="s">
-        <v>48</v>
+      <c r="AL42" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AM42" s="1" t="s">
         <v>49</v>
@@ -6276,13 +6282,13 @@
         <v>70</v>
       </c>
       <c r="G43" s="3">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="I43" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J43" s="3">
         <v>10</v>
@@ -6302,53 +6308,53 @@
       <c r="R43" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V43" s="1" t="s">
-        <v>49</v>
+      <c r="S43" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T43" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U43" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="W43" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="X43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA43" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB43" s="1" t="s">
-        <v>49</v>
+      <c r="X43" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y43" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z43" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB43" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AC43" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE43" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF43" s="2" t="s">
-        <v>48</v>
+      <c r="AD43" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF43" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AG43" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH43" s="2" t="s">
-        <v>48</v>
+      <c r="AH43" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AI43" s="2" t="s">
         <v>48</v>
@@ -6356,14 +6362,14 @@
       <c r="AJ43" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AK43" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AL43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM43" s="2" t="s">
-        <v>48</v>
+      <c r="AK43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL43" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM43" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AN43" s="1" t="s">
         <v>49</v>
@@ -6377,40 +6383,40 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="3">
+        <v>10</v>
+      </c>
+      <c r="E44" s="3">
+        <v>70</v>
+      </c>
+      <c r="G44" s="3">
+        <v>130</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D44" s="3">
-        <v>-30</v>
-      </c>
-      <c r="E44" s="3">
-        <v>80</v>
-      </c>
-      <c r="G44" s="3">
-        <v>190</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>147</v>
+      <c r="I44" s="3">
+        <v>30</v>
       </c>
       <c r="J44" s="3">
-        <v>35</v>
-      </c>
-      <c r="K44" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q44" s="2" t="s">
         <v>48</v>
@@ -6430,8 +6436,8 @@
       <c r="V44" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="W44" s="1" t="s">
-        <v>49</v>
+      <c r="W44" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="X44" s="1" t="s">
         <v>49</v>
@@ -6442,8 +6448,8 @@
       <c r="Z44" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AA44" s="1" t="s">
-        <v>49</v>
+      <c r="AA44" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AB44" s="1" t="s">
         <v>49</v>
@@ -6454,32 +6460,32 @@
       <c r="AD44" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AE44" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF44" s="1" t="s">
-        <v>49</v>
+      <c r="AE44" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF44" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AG44" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH44" s="1" t="s">
-        <v>49</v>
+      <c r="AH44" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AI44" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ44" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK44" s="1" t="s">
-        <v>49</v>
+      <c r="AJ44" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK44" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AL44" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AM44" s="1" t="s">
-        <v>49</v>
+      <c r="AM44" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AN44" s="1" t="s">
         <v>49</v>
@@ -6493,35 +6499,35 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="3">
+        <v>-30</v>
+      </c>
+      <c r="E45" s="3">
+        <v>80</v>
+      </c>
+      <c r="G45" s="3">
+        <v>190</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J45" s="3">
+        <v>35</v>
+      </c>
+      <c r="K45" s="3">
+        <v>16</v>
+      </c>
+      <c r="M45" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D45" s="3">
-        <v>10</v>
-      </c>
-      <c r="E45" s="3">
-        <v>70</v>
-      </c>
-      <c r="G45" s="3">
-        <v>150</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="I45" s="3">
-        <v>23</v>
-      </c>
-      <c r="J45" s="3">
-        <v>10</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="O45" s="1" t="s">
         <v>49</v>
       </c>
@@ -6534,17 +6540,17 @@
       <c r="R45" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S45" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T45" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U45" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V45" s="2" t="s">
-        <v>48</v>
+      <c r="S45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V45" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="W45" s="1" t="s">
         <v>49</v>
@@ -6552,14 +6558,14 @@
       <c r="X45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Y45" s="2" t="s">
-        <v>48</v>
+      <c r="Y45" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Z45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AA45" s="2" t="s">
-        <v>48</v>
+      <c r="AA45" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AB45" s="1" t="s">
         <v>49</v>
@@ -6567,20 +6573,20 @@
       <c r="AC45" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD45" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE45" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF45" s="2" t="s">
-        <v>48</v>
+      <c r="AD45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF45" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AG45" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH45" s="2" t="s">
-        <v>48</v>
+      <c r="AH45" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AI45" s="2" t="s">
         <v>48</v>
@@ -6588,17 +6594,17 @@
       <c r="AJ45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AK45" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AL45" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AM45" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AN45" s="2" t="s">
-        <v>48</v>
+      <c r="AK45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN45" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AO45" s="2" t="s">
         <v>48</v>
@@ -6609,13 +6615,13 @@
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D46" s="3">
         <v>10</v>
@@ -6624,13 +6630,13 @@
         <v>70</v>
       </c>
       <c r="G46" s="3">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="I46" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J46" s="3">
         <v>10</v>
@@ -6638,11 +6644,11 @@
       <c r="M46" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O46" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P46" s="2" t="s">
-        <v>48</v>
+      <c r="O46" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q46" s="2" t="s">
         <v>48</v>
@@ -6650,41 +6656,41 @@
       <c r="R46" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S46" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T46" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U46" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V46" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="W46" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X46" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y46" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z46" s="2" t="s">
-        <v>48</v>
+      <c r="S46" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T46" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U46" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V46" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W46" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X46" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y46" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z46" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AA46" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB46" s="2" t="s">
-        <v>48</v>
+      <c r="AB46" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AC46" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD46" s="1" t="s">
-        <v>49</v>
+      <c r="AD46" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AE46" s="2" t="s">
         <v>48</v>
@@ -6701,20 +6707,20 @@
       <c r="AI46" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ46" s="2" t="s">
-        <v>48</v>
+      <c r="AJ46" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AK46" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AL46" s="1" t="s">
-        <v>49</v>
+      <c r="AL46" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AM46" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AN46" s="1" t="s">
-        <v>49</v>
+      <c r="AN46" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AO46" s="2" t="s">
         <v>48</v>
@@ -6740,13 +6746,13 @@
         <v>70</v>
       </c>
       <c r="G47" s="3">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="I47" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J47" s="3">
         <v>10</v>
@@ -6754,11 +6760,11 @@
       <c r="M47" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O47" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P47" s="1" t="s">
-        <v>49</v>
+      <c r="O47" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q47" s="2" t="s">
         <v>48</v>
@@ -6766,32 +6772,32 @@
       <c r="R47" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S47" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T47" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U47" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V47" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W47" s="1" t="s">
-        <v>49</v>
+      <c r="S47" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T47" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U47" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V47" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W47" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="X47" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y47" s="2" t="s">
-        <v>48</v>
+      <c r="Y47" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Z47" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA47" s="1" t="s">
-        <v>49</v>
+      <c r="AA47" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AB47" s="2" t="s">
         <v>48</v>
@@ -6799,38 +6805,38 @@
       <c r="AC47" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD47" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE47" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF47" s="1" t="s">
-        <v>49</v>
+      <c r="AD47" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE47" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF47" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AG47" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH47" s="1" t="s">
-        <v>49</v>
+      <c r="AH47" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AI47" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ47" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK47" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AL47" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AM47" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AN47" s="2" t="s">
-        <v>48</v>
+      <c r="AJ47" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK47" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL47" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM47" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN47" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AO47" s="2" t="s">
         <v>48</v>
@@ -6856,10 +6862,10 @@
         <v>70</v>
       </c>
       <c r="G48" s="3">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="I48" s="3">
         <v>24</v>
@@ -6882,17 +6888,17 @@
       <c r="R48" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S48" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T48" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U48" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V48" s="1" t="s">
-        <v>49</v>
+      <c r="S48" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T48" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U48" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V48" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="W48" s="1" t="s">
         <v>49</v>
@@ -6900,14 +6906,14 @@
       <c r="X48" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y48" s="1" t="s">
-        <v>49</v>
+      <c r="Y48" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA48" s="2" t="s">
-        <v>48</v>
+      <c r="AA48" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AB48" s="2" t="s">
         <v>48</v>
@@ -6915,20 +6921,20 @@
       <c r="AC48" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD48" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE48" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF48" s="2" t="s">
-        <v>48</v>
+      <c r="AD48" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE48" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF48" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AG48" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH48" s="2" t="s">
-        <v>48</v>
+      <c r="AH48" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AI48" s="2" t="s">
         <v>48</v>
@@ -6936,17 +6942,17 @@
       <c r="AJ48" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AK48" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AL48" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM48" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AN48" s="1" t="s">
-        <v>49</v>
+      <c r="AK48" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL48" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM48" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN48" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AO48" s="2" t="s">
         <v>48</v>
@@ -6972,13 +6978,13 @@
         <v>70</v>
       </c>
       <c r="G49" s="3">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>147</v>
       </c>
       <c r="I49" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J49" s="3">
         <v>10</v>
@@ -6998,17 +7004,17 @@
       <c r="R49" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S49" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T49" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U49" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V49" s="2" t="s">
-        <v>48</v>
+      <c r="S49" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T49" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U49" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V49" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="W49" s="1" t="s">
         <v>49</v>
@@ -7016,14 +7022,14 @@
       <c r="X49" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y49" s="2" t="s">
-        <v>48</v>
+      <c r="Y49" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Z49" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA49" s="1" t="s">
-        <v>49</v>
+      <c r="AA49" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AB49" s="2" t="s">
         <v>48</v>
@@ -7031,20 +7037,20 @@
       <c r="AC49" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD49" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE49" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF49" s="1" t="s">
-        <v>49</v>
+      <c r="AD49" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE49" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF49" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AG49" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH49" s="1" t="s">
-        <v>49</v>
+      <c r="AH49" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AI49" s="2" t="s">
         <v>48</v>
@@ -7052,17 +7058,17 @@
       <c r="AJ49" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AK49" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AL49" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AM49" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AN49" s="2" t="s">
-        <v>48</v>
+      <c r="AK49" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL49" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM49" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN49" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AO49" s="2" t="s">
         <v>48</v>
@@ -7088,10 +7094,10 @@
         <v>70</v>
       </c>
       <c r="G50" s="3">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="I50" s="3">
         <v>21</v>
@@ -7102,11 +7108,11 @@
       <c r="M50" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O50" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P50" s="2" t="s">
-        <v>48</v>
+      <c r="O50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q50" s="2" t="s">
         <v>48</v>
@@ -7114,32 +7120,32 @@
       <c r="R50" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="W50" s="2" t="s">
-        <v>48</v>
+      <c r="S50" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T50" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U50" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V50" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W50" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="X50" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y50" s="1" t="s">
-        <v>49</v>
+      <c r="Y50" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Z50" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA50" s="2" t="s">
-        <v>48</v>
+      <c r="AA50" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AB50" s="2" t="s">
         <v>48</v>
@@ -7147,38 +7153,38 @@
       <c r="AC50" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE50" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF50" s="2" t="s">
-        <v>48</v>
+      <c r="AD50" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF50" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AG50" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH50" s="2" t="s">
-        <v>48</v>
+      <c r="AH50" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AI50" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ50" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK50" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AL50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM50" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AN50" s="1" t="s">
-        <v>49</v>
+      <c r="AJ50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL50" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN50" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AO50" s="2" t="s">
         <v>48</v>
@@ -7189,40 +7195,40 @@
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="D51" s="3">
-        <v>-30</v>
+        <v>10</v>
       </c>
       <c r="E51" s="3">
         <v>70</v>
       </c>
       <c r="G51" s="3">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>147</v>
+        <v>172</v>
+      </c>
+      <c r="I51" s="3">
+        <v>21</v>
       </c>
       <c r="J51" s="3">
-        <v>30</v>
-      </c>
-      <c r="K51" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M51" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O51" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>49</v>
+      <c r="O51" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q51" s="2" t="s">
         <v>48</v>
@@ -7230,26 +7236,26 @@
       <c r="R51" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S51" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T51" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U51" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V51" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W51" s="1" t="s">
-        <v>49</v>
+      <c r="S51" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T51" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U51" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V51" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W51" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="X51" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y51" s="2" t="s">
-        <v>48</v>
+      <c r="Y51" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Z51" s="2" t="s">
         <v>48</v>
@@ -7263,8 +7269,8 @@
       <c r="AC51" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD51" s="2" t="s">
-        <v>48</v>
+      <c r="AD51" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AE51" s="2" t="s">
         <v>48</v>
@@ -7281,20 +7287,20 @@
       <c r="AI51" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ51" s="1" t="s">
-        <v>49</v>
+      <c r="AJ51" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AK51" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AL51" s="2" t="s">
-        <v>48</v>
+      <c r="AL51" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AM51" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AN51" s="2" t="s">
-        <v>48</v>
+      <c r="AN51" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AO51" s="2" t="s">
         <v>48</v>
@@ -7308,13 +7314,13 @@
         <v>173</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>174</v>
       </c>
       <c r="D52" s="3">
-        <v>10</v>
+        <v>-30</v>
       </c>
       <c r="E52" s="3">
         <v>70</v>
@@ -7323,16 +7329,16 @@
         <v>190</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="I52" s="3">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="J52" s="3">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="K52" s="3">
+        <v>5</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="O52" s="1" t="s">
         <v>49</v>
@@ -7346,53 +7352,53 @@
       <c r="R52" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V52" s="1" t="s">
-        <v>49</v>
+      <c r="S52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="W52" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="X52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB52" s="1" t="s">
-        <v>49</v>
+      <c r="X52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB52" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AC52" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF52" s="1" t="s">
-        <v>49</v>
+      <c r="AD52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF52" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AG52" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH52" s="1" t="s">
-        <v>49</v>
+      <c r="AH52" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AI52" s="2" t="s">
         <v>48</v>
@@ -7400,17 +7406,17 @@
       <c r="AJ52" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AK52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AL52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AN52" s="1" t="s">
-        <v>49</v>
+      <c r="AK52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN52" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AO52" s="2" t="s">
         <v>48</v>
@@ -7421,13 +7427,13 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D53" s="3">
         <v>10</v>
@@ -7436,25 +7442,25 @@
         <v>70</v>
       </c>
       <c r="G53" s="3">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I53" s="3">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J53" s="3">
         <v>10</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="O53" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P53" s="2" t="s">
-        <v>48</v>
+        <v>178</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q53" s="2" t="s">
         <v>48</v>
@@ -7474,23 +7480,23 @@
       <c r="V53" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="W53" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X53" s="2" t="s">
-        <v>48</v>
+      <c r="W53" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X53" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Y53" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Z53" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA53" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB53" s="2" t="s">
-        <v>48</v>
+      <c r="Z53" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA53" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB53" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AC53" s="2" t="s">
         <v>48</v>
@@ -7498,32 +7504,32 @@
       <c r="AD53" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AE53" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF53" s="2" t="s">
-        <v>48</v>
+      <c r="AE53" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF53" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AG53" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH53" s="2" t="s">
-        <v>48</v>
+      <c r="AH53" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AI53" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ53" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK53" s="2" t="s">
-        <v>48</v>
+      <c r="AJ53" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK53" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AL53" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AM53" s="2" t="s">
-        <v>48</v>
+      <c r="AM53" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AN53" s="1" t="s">
         <v>49</v>
@@ -7537,13 +7543,13 @@
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D54" s="3">
         <v>10</v>
@@ -7552,16 +7558,16 @@
         <v>70</v>
       </c>
       <c r="G54" s="3">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I54" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J54" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M54" s="3" t="s">
         <v>47</v>
@@ -7602,8 +7608,8 @@
       <c r="Z54" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA54" s="1" t="s">
-        <v>49</v>
+      <c r="AA54" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AB54" s="2" t="s">
         <v>48</v>
@@ -7614,17 +7620,17 @@
       <c r="AD54" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AE54" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF54" s="1" t="s">
-        <v>49</v>
+      <c r="AE54" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF54" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AG54" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH54" s="1" t="s">
-        <v>49</v>
+      <c r="AH54" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AI54" s="2" t="s">
         <v>48</v>
@@ -7632,14 +7638,14 @@
       <c r="AJ54" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AK54" s="1" t="s">
-        <v>49</v>
+      <c r="AK54" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AL54" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AM54" s="1" t="s">
-        <v>49</v>
+      <c r="AM54" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AN54" s="1" t="s">
         <v>49</v>
@@ -7668,25 +7674,25 @@
         <v>70</v>
       </c>
       <c r="G55" s="3">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>73</v>
+        <v>172</v>
       </c>
       <c r="I55" s="3">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J55" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P55" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q55" s="2" t="s">
         <v>48</v>
@@ -7706,23 +7712,23 @@
       <c r="V55" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="W55" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="X55" s="1" t="s">
-        <v>49</v>
+      <c r="W55" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X55" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Y55" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Z55" s="1" t="s">
-        <v>49</v>
+      <c r="Z55" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AA55" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AB55" s="1" t="s">
-        <v>49</v>
+      <c r="AB55" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AC55" s="2" t="s">
         <v>48</v>
@@ -7745,8 +7751,8 @@
       <c r="AI55" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ55" s="1" t="s">
-        <v>49</v>
+      <c r="AJ55" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AK55" s="1" t="s">
         <v>49</v>
@@ -7772,7 +7778,7 @@
         <v>184</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>185</v>
@@ -7784,22 +7790,19 @@
         <v>70</v>
       </c>
       <c r="G56" s="3">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>147</v>
+        <v>73</v>
+      </c>
+      <c r="I56" s="3">
+        <v>32</v>
       </c>
       <c r="J56" s="3">
-        <v>60</v>
-      </c>
-      <c r="K56" s="3">
         <v>10</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N56" s="3" t="s">
-        <v>186</v>
+        <v>83</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>49</v>
@@ -7813,41 +7816,41 @@
       <c r="R56" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S56" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T56" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U56" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V56" s="2" t="s">
-        <v>48</v>
+      <c r="S56" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T56" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U56" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V56" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="W56" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="X56" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y56" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z56" s="2" t="s">
-        <v>48</v>
+      <c r="X56" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y56" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z56" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AA56" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AB56" s="2" t="s">
-        <v>48</v>
+      <c r="AB56" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AC56" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD56" s="2" t="s">
-        <v>48</v>
+      <c r="AD56" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AE56" s="1" t="s">
         <v>49</v>
@@ -7870,14 +7873,14 @@
       <c r="AK56" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AL56" s="2" t="s">
-        <v>48</v>
+      <c r="AL56" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AM56" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AN56" s="2" t="s">
-        <v>48</v>
+      <c r="AN56" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AO56" s="2" t="s">
         <v>48</v>
@@ -7888,43 +7891,46 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="D57" s="3">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="E57" s="3">
-        <v>1</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="G57" s="3">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I57" s="3">
-        <v>34</v>
+        <v>147</v>
+      </c>
+      <c r="J57" s="3">
+        <v>60</v>
+      </c>
+      <c r="K57" s="3">
+        <v>10</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O57" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P57" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>49</v>
+      <c r="N57" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="R57" s="2" t="s">
         <v>48</v>
@@ -7941,8 +7947,8 @@
       <c r="V57" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="W57" s="2" t="s">
-        <v>48</v>
+      <c r="W57" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="X57" s="2" t="s">
         <v>48</v>
@@ -7953,44 +7959,44 @@
       <c r="Z57" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA57" s="2" t="s">
-        <v>48</v>
+      <c r="AA57" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AB57" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AC57" s="1" t="s">
-        <v>49</v>
+      <c r="AC57" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AD57" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AE57" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF57" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AG57" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AH57" s="2" t="s">
-        <v>48</v>
+      <c r="AE57" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF57" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AG57" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH57" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AI57" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ57" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK57" s="2" t="s">
-        <v>48</v>
+      <c r="AJ57" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK57" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AL57" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AM57" s="2" t="s">
-        <v>48</v>
+      <c r="AM57" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AN57" s="2" t="s">
         <v>48</v>
@@ -8022,7 +8028,7 @@
         <v>49</v>
       </c>
       <c r="G58" s="3">
-        <v>270</v>
+        <v>190</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>76</v>
@@ -8031,7 +8037,7 @@
         <v>34</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>48</v>
@@ -8042,8 +8048,8 @@
       <c r="Q58" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R58" s="1" t="s">
-        <v>49</v>
+      <c r="R58" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="S58" s="2" t="s">
         <v>48</v>
@@ -8093,8 +8099,8 @@
       <c r="AH58" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AI58" s="1" t="s">
-        <v>49</v>
+      <c r="AI58" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AJ58" s="2" t="s">
         <v>48</v>
@@ -8111,11 +8117,11 @@
       <c r="AN58" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AO58" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AP58" s="1" t="s">
-        <v>49</v>
+      <c r="AO58" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP58" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="59">
@@ -8138,7 +8144,7 @@
         <v>49</v>
       </c>
       <c r="G59" s="3">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>76</v>
@@ -8147,7 +8153,7 @@
         <v>34</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>47</v>
+        <v>150</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>48</v>
@@ -8155,8 +8161,8 @@
       <c r="P59" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Q59" s="2" t="s">
-        <v>48</v>
+      <c r="Q59" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="R59" s="1" t="s">
         <v>49</v>
@@ -8191,8 +8197,8 @@
       <c r="AB59" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AC59" s="2" t="s">
-        <v>48</v>
+      <c r="AC59" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AD59" s="2" t="s">
         <v>48</v>
@@ -8203,8 +8209,8 @@
       <c r="AF59" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AG59" s="2" t="s">
-        <v>48</v>
+      <c r="AG59" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AH59" s="2" t="s">
         <v>48</v>
@@ -8254,13 +8260,13 @@
         <v>49</v>
       </c>
       <c r="G60" s="3">
-        <v>270</v>
+        <v>190</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="I60" s="3">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>47</v>
@@ -8271,8 +8277,8 @@
       <c r="P60" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Q60" s="1" t="s">
-        <v>49</v>
+      <c r="Q60" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="R60" s="1" t="s">
         <v>49</v>
@@ -8307,8 +8313,8 @@
       <c r="AB60" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AC60" s="1" t="s">
-        <v>49</v>
+      <c r="AC60" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AD60" s="2" t="s">
         <v>48</v>
@@ -8319,8 +8325,8 @@
       <c r="AF60" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AG60" s="1" t="s">
-        <v>49</v>
+      <c r="AG60" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AH60" s="2" t="s">
         <v>48</v>
@@ -8352,67 +8358,67 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="D61" s="3">
-        <v>-30</v>
+        <v>-5</v>
       </c>
       <c r="E61" s="3">
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>49</v>
       </c>
       <c r="G61" s="3">
-        <v>70</v>
+        <v>270</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>68</v>
+        <v>197</v>
       </c>
       <c r="I61" s="3">
         <v>15</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P61" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q61" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="R61" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="S61" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T61" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U61" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V61" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="W61" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R61" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S61" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T61" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U61" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W61" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="X61" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y61" s="1" t="s">
-        <v>49</v>
+      <c r="Y61" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Z61" s="2" t="s">
         <v>48</v>
@@ -8423,11 +8429,11 @@
       <c r="AB61" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AC61" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD61" s="1" t="s">
-        <v>49</v>
+      <c r="AC61" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD61" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AE61" s="2" t="s">
         <v>48</v>
@@ -8435,35 +8441,35 @@
       <c r="AF61" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AG61" s="2" t="s">
-        <v>48</v>
+      <c r="AG61" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AH61" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AI61" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AJ61" s="1" t="s">
-        <v>49</v>
+      <c r="AI61" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ61" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AK61" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AL61" s="1" t="s">
-        <v>49</v>
+      <c r="AL61" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AM61" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AN61" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AO61" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AP61" s="2" t="s">
-        <v>48</v>
+      <c r="AN61" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO61" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP61" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="62">
@@ -8474,34 +8480,34 @@
         <v>44</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="D62" s="3">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="E62" s="3">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>49</v>
       </c>
       <c r="G62" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>200</v>
+        <v>68</v>
       </c>
       <c r="I62" s="3">
         <v>15</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="O62" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P62" s="2" t="s">
-        <v>48</v>
+        <v>199</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q62" s="2" t="s">
         <v>48</v>
@@ -8521,8 +8527,8 @@
       <c r="V62" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="W62" s="2" t="s">
-        <v>48</v>
+      <c r="W62" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="X62" s="2" t="s">
         <v>48</v>
@@ -8560,8 +8566,8 @@
       <c r="AI62" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ62" s="2" t="s">
-        <v>48</v>
+      <c r="AJ62" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AK62" s="2" t="s">
         <v>48</v>
@@ -8572,8 +8578,8 @@
       <c r="AM62" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AN62" s="2" t="s">
-        <v>48</v>
+      <c r="AN62" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AO62" s="2" t="s">
         <v>48</v>
@@ -8584,40 +8590,40 @@
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D63" s="3">
         <v>-20</v>
       </c>
       <c r="E63" s="3">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>49</v>
       </c>
       <c r="G63" s="3">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="I63" s="3">
         <v>15</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P63" s="1" t="s">
-        <v>49</v>
+        <v>199</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q63" s="2" t="s">
         <v>48</v>
@@ -8625,32 +8631,32 @@
       <c r="R63" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S63" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T63" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U63" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V63" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W63" s="1" t="s">
-        <v>49</v>
+      <c r="S63" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T63" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U63" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V63" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W63" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="X63" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y63" s="2" t="s">
-        <v>48</v>
+      <c r="Y63" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Z63" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA63" s="1" t="s">
-        <v>49</v>
+      <c r="AA63" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AB63" s="2" t="s">
         <v>48</v>
@@ -8658,35 +8664,35 @@
       <c r="AC63" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD63" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE63" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF63" s="1" t="s">
-        <v>49</v>
+      <c r="AD63" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE63" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF63" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AG63" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH63" s="1" t="s">
-        <v>49</v>
+      <c r="AH63" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AI63" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ63" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK63" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AL63" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AM63" s="1" t="s">
-        <v>49</v>
+      <c r="AJ63" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK63" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL63" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM63" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AN63" s="2" t="s">
         <v>48</v>
@@ -8718,10 +8724,10 @@
         <v>49</v>
       </c>
       <c r="G64" s="3">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>68</v>
+        <v>197</v>
       </c>
       <c r="I64" s="3">
         <v>15</v>
@@ -8765,8 +8771,8 @@
       <c r="Z64" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA64" s="2" t="s">
-        <v>48</v>
+      <c r="AA64" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AB64" s="2" t="s">
         <v>48</v>
@@ -8777,17 +8783,17 @@
       <c r="AD64" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AE64" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF64" s="2" t="s">
-        <v>48</v>
+      <c r="AE64" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF64" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AG64" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH64" s="2" t="s">
-        <v>48</v>
+      <c r="AH64" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AI64" s="2" t="s">
         <v>48</v>
@@ -8795,14 +8801,14 @@
       <c r="AJ64" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AK64" s="2" t="s">
-        <v>48</v>
+      <c r="AK64" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AL64" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AM64" s="2" t="s">
-        <v>48</v>
+      <c r="AM64" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AN64" s="2" t="s">
         <v>48</v>
@@ -8834,10 +8840,10 @@
         <v>49</v>
       </c>
       <c r="G65" s="3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="I65" s="3">
         <v>15</v>
@@ -8950,10 +8956,10 @@
         <v>49</v>
       </c>
       <c r="G66" s="3">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="I66" s="3">
         <v>15</v>
@@ -8961,11 +8967,11 @@
       <c r="M66" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O66" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P66" s="2" t="s">
-        <v>48</v>
+      <c r="O66" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q66" s="2" t="s">
         <v>48</v>
@@ -8973,26 +8979,26 @@
       <c r="R66" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S66" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T66" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U66" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V66" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="W66" s="2" t="s">
-        <v>48</v>
+      <c r="S66" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T66" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U66" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W66" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="X66" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y66" s="1" t="s">
-        <v>49</v>
+      <c r="Y66" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Z66" s="2" t="s">
         <v>48</v>
@@ -9006,8 +9012,8 @@
       <c r="AC66" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD66" s="1" t="s">
-        <v>49</v>
+      <c r="AD66" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AE66" s="2" t="s">
         <v>48</v>
@@ -9024,20 +9030,20 @@
       <c r="AI66" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ66" s="2" t="s">
-        <v>48</v>
+      <c r="AJ66" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AK66" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AL66" s="1" t="s">
-        <v>49</v>
+      <c r="AL66" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AM66" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AN66" s="1" t="s">
-        <v>49</v>
+      <c r="AN66" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AO66" s="2" t="s">
         <v>48</v>
@@ -9182,10 +9188,10 @@
         <v>49</v>
       </c>
       <c r="G68" s="3">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="I68" s="3">
         <v>15</v>
@@ -9229,8 +9235,8 @@
       <c r="Z68" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA68" s="1" t="s">
-        <v>49</v>
+      <c r="AA68" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AB68" s="2" t="s">
         <v>48</v>
@@ -9241,17 +9247,17 @@
       <c r="AD68" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AE68" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF68" s="1" t="s">
-        <v>49</v>
+      <c r="AE68" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF68" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AG68" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH68" s="1" t="s">
-        <v>49</v>
+      <c r="AH68" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AI68" s="2" t="s">
         <v>48</v>
@@ -9259,14 +9265,14 @@
       <c r="AJ68" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AK68" s="1" t="s">
-        <v>49</v>
+      <c r="AK68" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AL68" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AM68" s="1" t="s">
-        <v>49</v>
+      <c r="AM68" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AN68" s="1" t="s">
         <v>49</v>
@@ -9298,22 +9304,22 @@
         <v>49</v>
       </c>
       <c r="G69" s="3">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="I69" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M69" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O69" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P69" s="1" t="s">
-        <v>49</v>
+      <c r="O69" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q69" s="2" t="s">
         <v>48</v>
@@ -9321,71 +9327,71 @@
       <c r="R69" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S69" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T69" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U69" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V69" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W69" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="X69" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y69" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z69" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA69" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB69" s="1" t="s">
-        <v>49</v>
+      <c r="S69" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T69" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U69" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V69" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W69" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X69" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y69" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z69" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA69" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB69" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AC69" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD69" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE69" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF69" s="2" t="s">
-        <v>48</v>
+      <c r="AD69" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE69" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF69" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AG69" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH69" s="2" t="s">
-        <v>48</v>
+      <c r="AH69" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AI69" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ69" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK69" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AL69" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AM69" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AN69" s="2" t="s">
-        <v>48</v>
+      <c r="AJ69" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK69" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL69" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM69" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN69" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AO69" s="2" t="s">
         <v>48</v>
@@ -9414,13 +9420,13 @@
         <v>49</v>
       </c>
       <c r="G70" s="3">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I70" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M70" s="3" t="s">
         <v>47</v>
@@ -9452,20 +9458,20 @@
       <c r="W70" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="X70" s="2" t="s">
-        <v>48</v>
+      <c r="X70" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Y70" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Z70" s="2" t="s">
-        <v>48</v>
+      <c r="Z70" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AA70" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB70" s="2" t="s">
-        <v>48</v>
+      <c r="AB70" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AC70" s="2" t="s">
         <v>48</v>
@@ -9530,10 +9536,10 @@
         <v>49</v>
       </c>
       <c r="G71" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="I71" s="3">
         <v>15</v>
@@ -9541,11 +9547,11 @@
       <c r="M71" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O71" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P71" s="2" t="s">
-        <v>48</v>
+      <c r="O71" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P71" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q71" s="2" t="s">
         <v>48</v>
@@ -9553,26 +9559,26 @@
       <c r="R71" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S71" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T71" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U71" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V71" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="W71" s="2" t="s">
-        <v>48</v>
+      <c r="S71" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T71" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U71" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V71" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W71" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="X71" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y71" s="1" t="s">
-        <v>49</v>
+      <c r="Y71" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Z71" s="2" t="s">
         <v>48</v>
@@ -9586,8 +9592,8 @@
       <c r="AC71" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD71" s="1" t="s">
-        <v>49</v>
+      <c r="AD71" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AE71" s="2" t="s">
         <v>48</v>
@@ -9604,20 +9610,20 @@
       <c r="AI71" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ71" s="2" t="s">
-        <v>48</v>
+      <c r="AJ71" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AK71" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AL71" s="1" t="s">
-        <v>49</v>
+      <c r="AL71" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AM71" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AN71" s="1" t="s">
-        <v>49</v>
+      <c r="AN71" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AO71" s="2" t="s">
         <v>48</v>
@@ -9646,22 +9652,22 @@
         <v>49</v>
       </c>
       <c r="G72" s="3">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="I72" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O72" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P72" s="1" t="s">
-        <v>49</v>
+      <c r="O72" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q72" s="2" t="s">
         <v>48</v>
@@ -9669,26 +9675,26 @@
       <c r="R72" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S72" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T72" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U72" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V72" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W72" s="1" t="s">
-        <v>49</v>
+      <c r="S72" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T72" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U72" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V72" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W72" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="X72" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y72" s="2" t="s">
-        <v>48</v>
+      <c r="Y72" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Z72" s="2" t="s">
         <v>48</v>
@@ -9702,8 +9708,8 @@
       <c r="AC72" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD72" s="2" t="s">
-        <v>48</v>
+      <c r="AD72" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AE72" s="2" t="s">
         <v>48</v>
@@ -9720,20 +9726,20 @@
       <c r="AI72" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ72" s="1" t="s">
-        <v>49</v>
+      <c r="AJ72" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AK72" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AL72" s="2" t="s">
-        <v>48</v>
+      <c r="AL72" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AM72" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AN72" s="2" t="s">
-        <v>48</v>
+      <c r="AN72" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AO72" s="2" t="s">
         <v>48</v>
@@ -9765,10 +9771,10 @@
         <v>80</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="I73" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M73" s="3" t="s">
         <v>47</v>
@@ -9800,20 +9806,20 @@
       <c r="W73" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="X73" s="1" t="s">
-        <v>49</v>
+      <c r="X73" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Y73" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Z73" s="1" t="s">
-        <v>49</v>
+      <c r="Z73" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AA73" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB73" s="1" t="s">
-        <v>49</v>
+      <c r="AB73" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AC73" s="2" t="s">
         <v>48</v>
@@ -9881,7 +9887,7 @@
         <v>80</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I74" s="3">
         <v>15</v>
@@ -9889,11 +9895,11 @@
       <c r="M74" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O74" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P74" s="2" t="s">
-        <v>48</v>
+      <c r="O74" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P74" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q74" s="2" t="s">
         <v>48</v>
@@ -9901,71 +9907,71 @@
       <c r="R74" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S74" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T74" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U74" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V74" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="W74" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X74" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y74" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z74" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA74" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB74" s="2" t="s">
-        <v>48</v>
+      <c r="S74" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T74" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U74" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V74" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W74" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X74" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y74" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z74" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA74" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB74" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AC74" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD74" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE74" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF74" s="1" t="s">
-        <v>49</v>
+      <c r="AD74" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE74" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF74" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AG74" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH74" s="1" t="s">
-        <v>49</v>
+      <c r="AH74" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AI74" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AJ74" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK74" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AL74" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM74" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AN74" s="1" t="s">
-        <v>49</v>
+      <c r="AJ74" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK74" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL74" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM74" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN74" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AO74" s="2" t="s">
         <v>48</v>
@@ -9994,10 +10000,10 @@
         <v>49</v>
       </c>
       <c r="G75" s="3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="I75" s="3">
         <v>15</v>
@@ -10017,41 +10023,41 @@
       <c r="R75" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S75" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T75" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U75" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V75" s="2" t="s">
-        <v>48</v>
+      <c r="S75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V75" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="W75" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="X75" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y75" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z75" s="1" t="s">
-        <v>49</v>
+      <c r="X75" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z75" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AA75" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AB75" s="1" t="s">
-        <v>49</v>
+      <c r="AB75" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AC75" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD75" s="2" t="s">
-        <v>48</v>
+      <c r="AD75" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AE75" s="1" t="s">
         <v>49</v>
@@ -10074,14 +10080,14 @@
       <c r="AK75" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AL75" s="2" t="s">
-        <v>48</v>
+      <c r="AL75" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AM75" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AN75" s="2" t="s">
-        <v>48</v>
+      <c r="AN75" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AO75" s="2" t="s">
         <v>48</v>
@@ -10110,10 +10116,10 @@
         <v>49</v>
       </c>
       <c r="G76" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="I76" s="3">
         <v>15</v>
@@ -10133,53 +10139,53 @@
       <c r="R76" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S76" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T76" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U76" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V76" s="1" t="s">
-        <v>49</v>
+      <c r="S76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V76" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="W76" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="X76" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y76" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z76" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA76" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB76" s="2" t="s">
-        <v>48</v>
+      <c r="X76" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z76" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA76" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB76" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AC76" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AD76" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE76" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF76" s="2" t="s">
-        <v>48</v>
+      <c r="AD76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE76" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF76" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AG76" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AH76" s="2" t="s">
-        <v>48</v>
+      <c r="AH76" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AI76" s="2" t="s">
         <v>48</v>
@@ -10187,22 +10193,138 @@
       <c r="AJ76" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AK76" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AL76" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM76" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AN76" s="1" t="s">
-        <v>49</v>
+      <c r="AK76" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM76" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN76" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AO76" s="2" t="s">
         <v>48</v>
       </c>
       <c r="AP76" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D77" s="3">
+        <v>-20</v>
+      </c>
+      <c r="E77" s="3">
+        <v>-5</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G77" s="3">
+        <v>90</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I77" s="3">
+        <v>15</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S77" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T77" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U77" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V77" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y77" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD77" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AJ77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL77" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN77" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP77" s="2" t="s">
         <v>48</v>
       </c>
     </row>
@@ -10357,13 +10479,13 @@
         <v>30</v>
       </c>
       <c r="AB1" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AC1" s="5" t="s">
         <v>34</v>
       </c>
       <c r="AD1" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AE1" s="5" t="s">
         <v>36</v>
@@ -10372,18 +10494,18 @@
         <v>38</v>
       </c>
       <c r="AG1" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D2" s="3">
         <v>-30</v>
@@ -10460,13 +10582,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D3" s="3">
         <v>-30</v>
@@ -10543,13 +10665,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D4" s="3">
         <v>-30</v>
@@ -10626,13 +10748,13 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D5" s="3">
         <v>0</v>
@@ -10644,7 +10766,7 @@
         <v>280</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I5" s="3">
         <v>65</v>
@@ -10712,13 +10834,13 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D6" s="3">
         <v>0</v>
@@ -10795,13 +10917,13 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D7" s="3">
         <v>-20</v>
@@ -10813,7 +10935,7 @@
         <v>350</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J7" s="3">
         <v>40</v>
@@ -10881,13 +11003,13 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D8" s="3">
         <v>0</v>
@@ -10899,7 +11021,7 @@
         <v>215</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I8" s="3">
         <v>55</v>
@@ -10964,13 +11086,13 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
@@ -11047,13 +11169,13 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D10" s="3">
         <v>0</v>
@@ -11130,13 +11252,13 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D11" s="3">
         <v>0</v>
@@ -11213,13 +11335,13 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D12" s="3">
         <v>0</v>
@@ -11299,13 +11421,13 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D13" s="3">
         <v>0</v>
@@ -11382,13 +11504,13 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
@@ -11465,13 +11587,13 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D15" s="3">
         <v>0</v>
@@ -11548,13 +11670,13 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D16" s="3">
         <v>0</v>
@@ -11631,13 +11753,13 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D17" s="3">
         <v>0</v>
@@ -11714,13 +11836,13 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D18" s="3">
         <v>0</v>
@@ -11732,7 +11854,7 @@
         <v>220</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I18" s="3">
         <v>20</v>
@@ -11797,13 +11919,13 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D19" s="3">
         <v>0</v>
@@ -11880,13 +12002,13 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D20" s="3">
         <v>0</v>
@@ -11966,13 +12088,13 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D21" s="3">
         <v>0</v>
@@ -12049,13 +12171,13 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
@@ -12132,13 +12254,13 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D23" s="3">
         <v>0</v>
@@ -12215,13 +12337,13 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
@@ -12233,7 +12355,7 @@
         <v>280</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I24" s="3">
         <v>50</v>
@@ -12298,13 +12420,13 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D25" s="3">
         <v>80</v>
@@ -12381,13 +12503,13 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D26" s="3">
         <v>80</v>
@@ -12464,13 +12586,13 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D27" s="3">
         <v>80</v>
@@ -12547,13 +12669,13 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D28" s="3">
         <v>80</v>
@@ -12630,13 +12752,13 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D29" s="3">
         <v>80</v>
@@ -12841,16 +12963,16 @@
         <v>26</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="V1" s="5" t="s">
         <v>28</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Y1" s="5" t="s">
         <v>36</v>
@@ -12858,13 +12980,13 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D2" s="3">
         <v>0</v>
@@ -12917,13 +13039,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D3" s="3">
         <v>0</v>
@@ -12935,7 +13057,7 @@
         <v>200</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I3" s="3">
         <v>40</v>
@@ -12976,13 +13098,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D4" s="3">
         <v>0</v>
@@ -12994,7 +13116,7 @@
         <v>260</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J4" s="3">
         <v>70</v>
@@ -13038,13 +13160,13 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D5" s="3">
         <v>10</v>
@@ -13097,13 +13219,13 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D6" s="3">
         <v>0</v>
@@ -13156,13 +13278,13 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D7" s="3">
         <v>10</v>
@@ -13174,7 +13296,7 @@
         <v>230</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I7" s="3">
         <v>30</v>
@@ -13215,13 +13337,13 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D8" s="3">
         <v>10</v>
@@ -13233,7 +13355,7 @@
         <v>230</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I8" s="3">
         <v>35</v>
@@ -13277,13 +13399,13 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D9" s="3">
         <v>5</v>
@@ -13295,7 +13417,7 @@
         <v>250</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I9" s="3">
         <v>45</v>
@@ -13336,13 +13458,13 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D10" s="3">
         <v>10</v>
@@ -13354,7 +13476,7 @@
         <v>170</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I10" s="3">
         <v>35</v>
@@ -13398,13 +13520,13 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D11" s="3">
         <v>0</v>
@@ -13460,13 +13582,13 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D12" s="3">
         <v>10</v>
@@ -13522,13 +13644,13 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D13" s="3">
         <v>0</v>
@@ -13581,13 +13703,13 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
@@ -13640,13 +13762,13 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D15" s="3">
         <v>5</v>
@@ -13658,7 +13780,7 @@
         <v>215</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I15" s="3">
         <v>30</v>
@@ -13699,13 +13821,13 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D16" s="3">
         <v>0</v>
@@ -13758,13 +13880,13 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D17" s="3">
         <v>0</v>
@@ -13776,7 +13898,7 @@
         <v>245</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I17" s="3">
         <v>35</v>
@@ -13817,13 +13939,13 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D18" s="3">
         <v>0</v>
@@ -13876,13 +13998,13 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D19" s="3">
         <v>20</v>
@@ -13935,13 +14057,13 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D20" s="3">
         <v>10</v>
@@ -13994,13 +14116,13 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D21" s="3">
         <v>20</v>
@@ -14053,13 +14175,13 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
@@ -14112,13 +14234,13 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D23" s="3">
         <v>0</v>
@@ -14130,7 +14252,7 @@
         <v>280</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I23" s="3">
         <v>28</v>
@@ -14174,13 +14296,13 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
@@ -14233,13 +14355,13 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D25" s="3">
         <v>20</v>
@@ -14251,7 +14373,7 @@
         <v>210</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I25" s="3">
         <v>30</v>
@@ -14292,13 +14414,13 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D26" s="3">
         <v>2</v>
@@ -14310,7 +14432,7 @@
         <v>205</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I26" s="3">
         <v>35</v>
@@ -14351,13 +14473,13 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D27" s="3">
         <v>50</v>
@@ -14410,13 +14532,13 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D28" s="3">
         <v>0</v>
@@ -14428,7 +14550,7 @@
         <v>210</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I28" s="3">
         <v>45</v>
@@ -14588,16 +14710,16 @@
         <v>16</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="S1" s="5" t="s">
         <v>24</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="U1" s="5" t="s">
         <v>26</v>
@@ -14626,13 +14748,13 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D2" s="3">
         <v>80</v>
@@ -14653,7 +14775,7 @@
         <v>10</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>48</v>
@@ -14697,13 +14819,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D3" s="3">
         <v>0</v>
@@ -14724,7 +14846,7 @@
         <v>15</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>49</v>
@@ -14768,13 +14890,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D4" s="3">
         <v>140</v>
@@ -14792,7 +14914,7 @@
         <v>27</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>48</v>
@@ -14836,13 +14958,13 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D5" s="3">
         <v>140</v>
@@ -14860,7 +14982,7 @@
         <v>29</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>48</v>
@@ -14904,13 +15026,13 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D6" s="3">
         <v>140</v>
@@ -14928,7 +15050,7 @@
         <v>25</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>48</v>
@@ -14972,13 +15094,13 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D7" s="3">
         <v>80</v>
@@ -14996,7 +15118,7 @@
         <v>27</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>48</v>
@@ -15040,13 +15162,13 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D8" s="3">
         <v>80</v>
@@ -15064,7 +15186,7 @@
         <v>27</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>48</v>
@@ -15108,13 +15230,13 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D9" s="3">
         <v>80</v>
@@ -15132,7 +15254,7 @@
         <v>25</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>48</v>
@@ -15176,13 +15298,13 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D10" s="3">
         <v>80</v>
@@ -15200,7 +15322,7 @@
         <v>25</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>48</v>
@@ -15244,13 +15366,13 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D11" s="3">
         <v>0</v>
@@ -15268,7 +15390,7 @@
         <v>23</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>49</v>
@@ -15312,13 +15434,13 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D12" s="3">
         <v>0</v>
@@ -15339,7 +15461,7 @@
         <v>10</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>49</v>
@@ -15383,13 +15505,13 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D13" s="3">
         <v>140</v>
@@ -15407,7 +15529,7 @@
         <v>31</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>48</v>
@@ -15451,13 +15573,13 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D14" s="3">
         <v>80</v>
@@ -15475,7 +15597,7 @@
         <v>29</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>48</v>
@@ -15519,13 +15641,13 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D15" s="3">
         <v>80</v>
@@ -15546,7 +15668,7 @@
         <v>8</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>48</v>
@@ -15590,13 +15712,13 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D16" s="3">
         <v>140</v>
@@ -15614,7 +15736,7 @@
         <v>27</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>48</v>
@@ -15658,13 +15780,13 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D17" s="3">
         <v>0</v>
@@ -15682,7 +15804,7 @@
         <v>25</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>49</v>
@@ -15726,13 +15848,13 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D18" s="3">
         <v>80</v>
@@ -15753,7 +15875,7 @@
         <v>8</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>48</v>
@@ -15797,13 +15919,13 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D19" s="3">
         <v>140</v>
@@ -15821,7 +15943,7 @@
         <v>27</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>48</v>
@@ -15865,13 +15987,13 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D20" s="3">
         <v>80</v>
@@ -15889,7 +16011,7 @@
         <v>25</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>48</v>
@@ -15933,13 +16055,13 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D21" s="3">
         <v>0</v>
@@ -15960,7 +16082,7 @@
         <v>10</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>49</v>
@@ -16004,13 +16126,13 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D22" s="3">
         <v>80</v>
@@ -16028,7 +16150,7 @@
         <v>25</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>48</v>
@@ -16072,13 +16194,13 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D23" s="3">
         <v>0</v>
@@ -16090,7 +16212,7 @@
         <v>30</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I23" s="3">
         <v>50</v>
@@ -16099,7 +16221,7 @@
         <v>10</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>49</v>
@@ -16143,13 +16265,13 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D24" s="3">
         <v>80</v>
@@ -16170,7 +16292,7 @@
         <v>15</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>48</v>
@@ -16214,13 +16336,13 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D25" s="3">
         <v>80</v>
@@ -16238,7 +16360,7 @@
         <v>23</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>48</v>
@@ -16282,13 +16404,13 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D26" s="3">
         <v>0</v>
@@ -16309,7 +16431,7 @@
         <v>12</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>49</v>
@@ -16353,13 +16475,13 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D27" s="3">
         <v>140</v>
@@ -16380,7 +16502,7 @@
         <v>10</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>48</v>
@@ -16424,13 +16546,13 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D28" s="3">
         <v>0</v>
@@ -16442,13 +16564,13 @@
         <v>10</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I28" s="3">
         <v>29</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O28" s="1" t="s">
         <v>49</v>
@@ -16492,13 +16614,13 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D29" s="3">
         <v>140</v>
@@ -16516,7 +16638,7 @@
         <v>25</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>48</v>
@@ -16560,13 +16682,13 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D30" s="3">
         <v>140</v>
@@ -16584,7 +16706,7 @@
         <v>25</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>48</v>
@@ -16750,30 +16872,30 @@
         <v>23</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="U1" s="5" t="s">
         <v>36</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D2" s="3">
         <v>40</v>
@@ -16823,13 +16945,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D3" s="3">
         <v>40</v>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -456,7 +456,7 @@
     <t>normal_amethyst</t>
   </si>
   <si>
-    <t>red_garnet 10 / almandine 15 / amethyst 40 / opal 40</t>
+    <t>amethyst 40 / opal 40 / red_garnet 10 / almandine 15</t>
   </si>
   <si>
     <t>28%</t>

--- a/OresToFieldGuide/data/sheet.xlsx
+++ b/OresToFieldGuide/data/sheet.xlsx
@@ -348,7 +348,7 @@
     <t>deep_scheelite</t>
   </si>
   <si>
-    <t>scheelite 12 / tungstate 12 / lithium 4 [1]</t>
+    <t>scheelite 12 / tungstate 12 / lepidolite 4 [1]</t>
   </si>
   <si>
     <t>deep_sphalerite</t>
@@ -1083,6 +1083,15 @@
     <t>#tfg:nether/is_tar_pools</t>
   </si>
   <si>
+    <t>beneath_lithium</t>
+  </si>
+  <si>
+    <t>spodumene 80 [1] / anthracite 30 / alunite 20</t>
+  </si>
+  <si>
+    <t>#tfg:nether/is_lava_floes</t>
+  </si>
+  <si>
     <t>beneath_bismuth</t>
   </si>
   <si>
@@ -1189,15 +1198,6 @@
   </si>
   <si>
     <t>#tfg:nether/is_salt_caves</t>
-  </si>
-  <si>
-    <t>beneath_lithium</t>
-  </si>
-  <si>
-    <t>spodumene 80 [1] / lithium 30 / rock_salt 20</t>
-  </si>
-  <si>
-    <t>#tfg:nether/is_lava_floes</t>
   </si>
   <si>
     <t>beneath_manganese</t>
@@ -14822,7 +14822,7 @@
         <v>355</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>356</v>
@@ -14837,13 +14837,10 @@
         <v>10</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J3" s="3">
-        <v>60</v>
-      </c>
-      <c r="K3" s="3">
-        <v>15</v>
+        <v>88</v>
+      </c>
+      <c r="I3" s="3">
+        <v>25</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>357</v>
@@ -14893,67 +14890,70 @@
         <v>358</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>359</v>
       </c>
       <c r="D4" s="3">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="G4" s="3">
         <v>10</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I4" s="3">
-        <v>27</v>
+        <v>76</v>
+      </c>
+      <c r="J4" s="3">
+        <v>60</v>
+      </c>
+      <c r="K4" s="3">
+        <v>15</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="O4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>48</v>
+      <c r="O4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>49</v>
+      <c r="R4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="T4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="U4" s="1" t="s">
-        <v>49</v>
+      <c r="U4" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="V4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="W4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>49</v>
+      <c r="W4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="5">
@@ -14976,10 +14976,10 @@
         <v>10</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="I5" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>363</v>
@@ -15044,10 +15044,10 @@
         <v>10</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="I6" s="3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>366</v>
@@ -15103,10 +15103,10 @@
         <v>368</v>
       </c>
       <c r="D7" s="3">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="E7" s="3">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="G7" s="3">
         <v>10</v>
@@ -15115,7 +15115,7 @@
         <v>46</v>
       </c>
       <c r="I7" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>369</v>
@@ -15135,26 +15135,26 @@
       <c r="S7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T7" s="1" t="s">
-        <v>49</v>
+      <c r="T7" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="U7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="V7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>48</v>
+      <c r="V7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Y7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>48</v>
+      <c r="Z7" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AA7" s="1" t="s">
         <v>49</v>
@@ -15180,7 +15180,7 @@
         <v>10</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="I8" s="3">
         <v>27</v>
@@ -15251,10 +15251,10 @@
         <v>147</v>
       </c>
       <c r="I9" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>48</v>
@@ -15298,13 +15298,13 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D10" s="3">
         <v>80</v>
@@ -15316,13 +15316,13 @@
         <v>10</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="I10" s="3">
         <v>25</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>48</v>
@@ -15366,55 +15366,55 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D11" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E11" s="3">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="G11" s="3">
         <v>10</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="I11" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>49</v>
+        <v>372</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>48</v>
+      <c r="R11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>48</v>
@@ -15422,25 +15422,25 @@
       <c r="X11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y11" s="2" t="s">
-        <v>48</v>
+      <c r="Y11" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Z11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AA11" s="2" t="s">
-        <v>48</v>
+      <c r="AA11" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D12" s="3">
         <v>0</v>
@@ -15452,16 +15452,13 @@
         <v>10</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="I12" s="3">
-        <v>50</v>
-      </c>
-      <c r="J12" s="3">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>381</v>
+        <v>360</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>49</v>
@@ -15508,84 +15505,87 @@
         <v>382</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>383</v>
       </c>
       <c r="D13" s="3">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="E13" s="3">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3">
         <v>10</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="I13" s="3">
-        <v>31</v>
+        <v>50</v>
+      </c>
+      <c r="J13" s="3">
+        <v>10</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>48</v>
+        <v>384</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Q13" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>49</v>
+      <c r="R13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="U13" s="1" t="s">
-        <v>49</v>
+      <c r="U13" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="V13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="W13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="X13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA13" s="1" t="s">
-        <v>49</v>
+      <c r="W13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA13" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D14" s="3">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="E14" s="3">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="G14" s="3">
         <v>10</v>
@@ -15594,10 +15594,10 @@
         <v>147</v>
       </c>
       <c r="I14" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>48</v>
@@ -15614,26 +15614,26 @@
       <c r="S14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T14" s="1" t="s">
-        <v>49</v>
+      <c r="T14" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="U14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="V14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="W14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>48</v>
+      <c r="V14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="Y14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Z14" s="2" t="s">
-        <v>48</v>
+      <c r="Z14" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="AA14" s="1" t="s">
         <v>49</v>
@@ -15641,13 +15641,13 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D15" s="3">
         <v>80</v>
@@ -15661,14 +15661,11 @@
       <c r="H15" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J15" s="3">
-        <v>60</v>
-      </c>
-      <c r="K15" s="3">
-        <v>8</v>
+      <c r="I15" s="3">
+        <v>29</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>48</v>
@@ -15712,31 +15709,34 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D16" s="3">
+        <v>80</v>
+      </c>
+      <c r="E16" s="3">
         <v>140</v>
       </c>
-      <c r="E16" s="3">
-        <v>190</v>
-      </c>
       <c r="G16" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="I16" s="3">
-        <v>27</v>
+        <v>147</v>
+      </c>
+      <c r="J16" s="3">
+        <v>60</v>
+      </c>
+      <c r="K16" s="3">
+        <v>8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>48</v>
@@ -15753,26 +15753,26 @@
       <c r="S16" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T16" s="2" t="s">
-        <v>48</v>
+      <c r="T16" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="U16" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="V16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="X16" s="1" t="s">
-        <v>49</v>
+      <c r="V16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Y16" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Z16" s="1" t="s">
-        <v>49</v>
+      <c r="Z16" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="AA16" s="1" t="s">
         <v>49</v>
@@ -15789,61 +15789,61 @@
         <v>392</v>
       </c>
       <c r="D17" s="3">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="E17" s="3">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="G17" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>88</v>
       </c>
       <c r="I17" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="O17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>49</v>
+      <c r="O17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q17" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>48</v>
+      <c r="R17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="T17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="U17" s="2" t="s">
-        <v>48</v>
+      <c r="U17" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="V17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="W17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA17" s="2" t="s">
-        <v>48</v>
+      <c r="W17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA17" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -15943,7 +15943,7 @@
         <v>27</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>48</v>
@@ -16082,7 +16082,7 @@
         <v>10</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>49</v>
@@ -16221,7 +16221,7 @@
         <v>10</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>393</v>
+        <v>357</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>49</v>
@@ -16360,7 +16360,7 @@
         <v>23</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>48</v>
@@ -16431,7 +16431,7 @@
         <v>12</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>49</v>
@@ -16502,7 +16502,7 @@
         <v>10</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>48</v>
@@ -16570,7 +16570,7 @@
         <v>29</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>393</v>
+        <v>357</v>
       </c>
       <c r="O28" s="1" t="s">
         <v>49</v>
@@ -16638,7 +16638,7 @@
         <v>25</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>48</v>
@@ -16706,7 +16706,7 @@
         <v>25</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>48</v>
